--- a/config/swarm-disaster-generated/templates/SwarmDisasterProgression.xlsx
+++ b/config/swarm-disaster-generated/templates/SwarmDisasterProgression.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="156">
   <si>
     <t>@table</t>
   </si>
@@ -184,7 +184,7 @@
     <t>SwarmDisasterPathstriderCabinet</t>
   </si>
   <si>
-    <t>84c6d76854b14a9b</t>
+    <t>3291b7193d17dd99</t>
   </si>
   <si>
     <t>sort</t>
@@ -205,27 +205,27 @@
     <t>description_parameters</t>
   </si>
   <si>
-    <t>ref&lt;SwarmDisasterPathObjective.id&gt;</t>
+    <t>range=0..1000</t>
+  </si>
+  <si>
+    <t>SwarmDisasterCommuningDimension</t>
+  </si>
+  <si>
+    <t>e7732cb01ac26da5</t>
+  </si>
+  <si>
+    <t>max_points</t>
+  </si>
+  <si>
+    <t>carry_policy</t>
+  </si>
+  <si>
+    <t>clamp_policy</t>
   </si>
   <si>
     <t>range=0..100</t>
   </si>
   <si>
-    <t>SwarmDisasterCommuningDimension</t>
-  </si>
-  <si>
-    <t>e7732cb01ac26da5</t>
-  </si>
-  <si>
-    <t>max_points</t>
-  </si>
-  <si>
-    <t>carry_policy</t>
-  </si>
-  <si>
-    <t>clamp_policy</t>
-  </si>
-  <si>
     <t>length=1..160</t>
   </si>
   <si>
@@ -313,7 +313,7 @@
     <t>SwarmDisasterPathObjective</t>
   </si>
   <si>
-    <t>443314995330a465</t>
+    <t>86abb6c229daf0ee</t>
   </si>
   <si>
     <t>cabinet_id</t>
@@ -334,49 +334,49 @@
     <t>ref&lt;SwarmDisasterPathstriderCabinet.id&gt;</t>
   </si>
   <si>
+    <t>SwarmDisasterPathstriderFinish</t>
+  </si>
+  <si>
+    <t>5f93b09e144c8f12</t>
+  </si>
+  <si>
+    <t>finish_type</t>
+  </si>
+  <si>
+    <t>comparison</t>
+  </si>
+  <si>
+    <t>parameters_json</t>
+  </si>
+  <si>
+    <t>target_progress</t>
+  </si>
+  <si>
+    <t>mode_hint</t>
+  </si>
+  <si>
+    <t>enabled_for_swarm_compilation</t>
+  </si>
+  <si>
+    <t>SwarmDisasterPathstriderUnlock</t>
+  </si>
+  <si>
+    <t>bb1ad3b4956d2d80</t>
+  </si>
+  <si>
+    <t>unlock_consequence_json</t>
+  </si>
+  <si>
+    <t>evaluation_boundary</t>
+  </si>
+  <si>
     <t>ref&lt;SwarmDisasterPathstriderFinish.id&gt;</t>
   </si>
   <si>
-    <t>SwarmDisasterPathstriderFinish</t>
-  </si>
-  <si>
-    <t>5f93b09e144c8f12</t>
-  </si>
-  <si>
-    <t>finish_type</t>
-  </si>
-  <si>
-    <t>comparison</t>
-  </si>
-  <si>
-    <t>parameters_json</t>
-  </si>
-  <si>
-    <t>target_progress</t>
-  </si>
-  <si>
-    <t>mode_hint</t>
-  </si>
-  <si>
-    <t>enabled_for_swarm_compilation</t>
-  </si>
-  <si>
-    <t>SwarmDisasterPathstriderUnlock</t>
-  </si>
-  <si>
-    <t>bb1ad3b4956d2d80</t>
-  </si>
-  <si>
-    <t>unlock_consequence_json</t>
-  </si>
-  <si>
-    <t>evaluation_boundary</t>
-  </si>
-  <si>
     <t>SwarmDisasterMechanicalChapter</t>
   </si>
   <si>
-    <t>49b421653bbcbef6</t>
+    <t>d5e61c9967b9c03d</t>
   </si>
   <si>
     <t>layer</t>
@@ -391,13 +391,16 @@
     <t>optional&lt;ref&lt;SwarmDisasterCommuningDimension.id&gt;&gt;</t>
   </si>
   <si>
+    <t>optional&lt;string&gt;</t>
+  </si>
+  <si>
     <t>range=1..3</t>
   </si>
   <si>
     <t>SwarmDisasterPath</t>
   </si>
   <si>
-    <t>7086d28c801470ab</t>
+    <t>b6a4ab67a8b535da</t>
   </si>
   <si>
     <t>shared_path_id</t>
@@ -412,7 +415,7 @@
     <t>mode_unlock_id</t>
   </si>
   <si>
-    <t>propagation_unlock</t>
+    <t>propagation_unlock_json</t>
   </si>
   <si>
     <t>resonance_id</t>
@@ -1365,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1389,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -1442,13 +1445,13 @@
         <v>97</v>
       </c>
       <c r="Q2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="S2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1501,13 +1504,13 @@
         <v>97</v>
       </c>
       <c r="Q3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="S3" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1557,7 +1560,7 @@
         <v>34</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>34</v>
@@ -1737,7 +1740,7 @@
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
     <col min="15" max="16" width="12.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="32.7109375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="16.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="22.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1944,7 +1947,7 @@
         <v>119</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="S4" s="5" t="s">
         <v>34</v>
@@ -2050,12 +2053,10 @@
         <v>47</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q6" s="5"/>
-      <c r="R6" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
         <v>48</v>
       </c>
@@ -2124,8 +2125,8 @@
     <col min="16" max="16" width="14.7109375" style="5" customWidth="1"/>
     <col min="17" max="18" width="12.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="32.7109375" style="5" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="5" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" style="5" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" style="5" customWidth="1"/>
+    <col min="21" max="21" width="23.7109375" style="5" customWidth="1"/>
     <col min="22" max="22" width="30.7109375" style="5" customWidth="1"/>
     <col min="23" max="23" width="22.7109375" style="5" customWidth="1"/>
     <col min="24" max="24" width="24.7109375" style="5" customWidth="1"/>
@@ -2137,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2161,7 +2162,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="24" customHeight="1">
@@ -2211,34 +2212,34 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>52</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -2288,34 +2289,34 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>52</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -2374,16 +2375,16 @@
         <v>33</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="W4" s="5" t="s">
         <v>38</v>
@@ -2517,13 +2518,13 @@
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="S6" s="5"/>
-      <c r="T6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5" t="s">
         <v>46</v>
@@ -2565,7 +2566,7 @@
       <c r="Y7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
@@ -2585,9 +2586,6 @@
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 100." promptTitle="Integer range" prompt="Enter an integer from 0 to 100." sqref="R8:R1007">
       <formula1>0</formula1>
       <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="U8:U1007">
-      <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2621,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2645,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="24" customHeight="1">
@@ -2695,7 +2693,7 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>26</v>
@@ -2704,19 +2702,19 @@
         <v>77</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -2766,7 +2764,7 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>26</v>
@@ -2775,19 +2773,19 @@
         <v>77</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -2840,7 +2838,7 @@
         <v>34</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>33</v>
@@ -2977,7 +2975,7 @@
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>74</v>
@@ -3070,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3094,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3147,10 +3145,10 @@
         <v>26</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3203,10 +3201,10 @@
         <v>26</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3256,7 +3254,7 @@
         <v>34</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>34</v>
@@ -3437,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3461,7 +3459,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="24" customHeight="1">
@@ -3511,22 +3509,22 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -3576,22 +3574,22 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -3641,10 +3639,10 @@
         <v>34</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>34</v>
@@ -3847,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3871,7 +3869,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3921,13 +3919,13 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3977,13 +3975,13 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4205,7 +4203,7 @@
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
     <col min="15" max="17" width="12.7109375" style="5" customWidth="1"/>
     <col min="18" max="19" width="22.7109375" style="5" customWidth="1"/>
-    <col min="20" max="20" width="32.7109375" style="5" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="5" customWidth="1"/>
     <col min="21" max="21" width="17.7109375" style="5" customWidth="1"/>
     <col min="22" max="22" width="22.7109375" style="5" customWidth="1"/>
   </cols>
@@ -4437,7 +4435,7 @@
         <v>38</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>34</v>
@@ -4555,7 +4553,7 @@
         <v>47</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>43</v>
@@ -4566,7 +4564,9 @@
       <c r="S6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="T6" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="U6" s="5" t="s">
         <v>48</v>
       </c>
@@ -4615,9 +4615,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="SwarmDisasterEvidenceGrade enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 100." promptTitle="Integer range" prompt="Enter an integer from 0 to 100." sqref="P8:P1007">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 1000." promptTitle="Integer range" prompt="Enter an integer from 0 to 1000." sqref="P8:P1007">
       <formula1>0</formula1>
-      <formula2>100</formula2>
+      <formula2>1000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4669,7 +4669,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -4722,13 +4722,13 @@
         <v>26</v>
       </c>
       <c r="Q2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -4781,13 +4781,13 @@
         <v>26</v>
       </c>
       <c r="Q3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -4952,7 +4952,7 @@
         <v>42</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>65</v>
@@ -5118,7 +5118,7 @@
         <v>71</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>72</v>
@@ -5183,7 +5183,7 @@
         <v>71</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>72</v>
@@ -5363,7 +5363,7 @@
         <v>47</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>43</v>
@@ -6591,7 +6591,7 @@
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="32.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="12.7109375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="32.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="20.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="22.7109375" style="5" customWidth="1"/>
   </cols>
@@ -6796,7 +6796,7 @@
         <v>34</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>34</v>
@@ -6905,7 +6905,9 @@
       <c r="P6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="R6" s="5" t="s">
         <v>48</v>
       </c>
@@ -6981,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7005,7 +7007,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
@@ -7055,25 +7057,25 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>99</v>
       </c>
       <c r="U2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -7123,25 +7125,25 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="T3" s="5" t="s">
         <v>99</v>
       </c>
       <c r="U3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:22">
